--- a/comfortable_speed.xlsx
+++ b/comfortable_speed.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FuttoAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B7D571-5AD2-44EF-A118-512DDFA122AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B8C77C-6BB6-4A17-AC7E-118D09BF8FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FAD0BBB9-9FA6-49EF-9FBB-58039FCA0FAD}"/>
+    <workbookView xWindow="-19310" yWindow="-1300" windowWidth="19420" windowHeight="11500" xr2:uid="{FAD0BBB9-9FA6-49EF-9FBB-58039FCA0FAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="8">
   <si>
     <t>Sakai</t>
     <phoneticPr fontId="1"/>
@@ -54,6 +55,22 @@
   </si>
   <si>
     <t>task03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kanai</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Yorii</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Okumura</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hara</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -438,85 +455,388 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D6EEC-EB3D-4750-8DFA-23F2515A2107}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="8" max="8" width="12.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="C2">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="D2">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="E2">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F2">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G2">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+        <v>0.18</v>
+      </c>
+      <c r="H2">
+        <f>AVERAGE(B2:G2)</f>
+        <v>0.9966666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="C3">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="D3">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="E3">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="F3">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="G3">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+        <v>0.25</v>
+      </c>
+      <c r="H3">
+        <f>AVERAGE(B3:G3)</f>
+        <v>1.0816666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
+        <v>1.61</v>
+      </c>
+      <c r="C4">
+        <v>1.57</v>
+      </c>
+      <c r="D4">
+        <v>1.69</v>
+      </c>
+      <c r="E4">
+        <v>0.4</v>
+      </c>
+      <c r="F4">
+        <v>0.35</v>
+      </c>
+      <c r="G4">
+        <v>0.27</v>
+      </c>
+      <c r="H4">
+        <f>AVERAGE(B4:G4)</f>
+        <v>0.9816666666666668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>1.51</v>
+      </c>
+      <c r="C7">
+        <v>1.35</v>
+      </c>
+      <c r="D7">
+        <v>1.4</v>
+      </c>
+      <c r="E7">
+        <v>0.44</v>
+      </c>
+      <c r="F7">
+        <v>0.4</v>
+      </c>
+      <c r="G7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H7">
+        <f>AVERAGE(B7:G7)</f>
+        <v>0.94166666666666676</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="C8">
+        <v>1.6</v>
+      </c>
+      <c r="D8">
+        <v>1.55</v>
+      </c>
+      <c r="E8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H3:H19" si="0">AVERAGE(B8:G8)</f>
+        <v>1.0333333333333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>1.55</v>
+      </c>
+      <c r="C9">
+        <v>1.5</v>
+      </c>
+      <c r="D9">
+        <v>1.54</v>
+      </c>
+      <c r="E9">
+        <v>0.27</v>
+      </c>
+      <c r="F9">
+        <v>0.4</v>
+      </c>
+      <c r="G9">
+        <v>0.42</v>
+      </c>
+      <c r="H9">
+        <f>AVERAGE(B9:G9)</f>
+        <v>0.94666666666666666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>1.6</v>
+      </c>
+      <c r="C12">
+        <v>1.84</v>
+      </c>
+      <c r="D12">
+        <v>1.89</v>
+      </c>
+      <c r="E12">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F12">
+        <v>0.3</v>
+      </c>
+      <c r="G12">
+        <v>0.31</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>1.0383333333333333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>1.83</v>
+      </c>
+      <c r="C13">
+        <v>1.89</v>
+      </c>
+      <c r="D13">
+        <v>1.91</v>
+      </c>
+      <c r="E13">
+        <v>0.32</v>
+      </c>
+      <c r="F13">
+        <v>0.38</v>
+      </c>
+      <c r="G13">
+        <v>0.42</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>1.9</v>
+      </c>
+      <c r="C14">
+        <v>1.93</v>
+      </c>
+      <c r="D14">
+        <v>1.98</v>
+      </c>
+      <c r="E14">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F14">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G14">
+        <v>0.27</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>1.85</v>
+      </c>
+      <c r="C17">
+        <v>1.89</v>
+      </c>
+      <c r="D17">
+        <v>1.86</v>
+      </c>
+      <c r="E17">
+        <v>0.6</v>
+      </c>
+      <c r="F17">
+        <v>0.8</v>
+      </c>
+      <c r="G17">
+        <v>0.75</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>1.2916666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>1.91</v>
+      </c>
+      <c r="C18">
+        <v>1.92</v>
+      </c>
+      <c r="D18">
         <v>1.87</v>
       </c>
-      <c r="C4">
-        <v>1.93</v>
-      </c>
-      <c r="D4">
-        <v>1.95</v>
-      </c>
-      <c r="E4">
-        <v>0.27</v>
-      </c>
-      <c r="F4">
-        <v>0.22</v>
-      </c>
-      <c r="G4">
-        <v>0.25</v>
+      <c r="E18">
+        <v>0.65</v>
+      </c>
+      <c r="F18">
+        <v>0.65</v>
+      </c>
+      <c r="G18">
+        <v>0.6</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>1.2666666666666668</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>1.87</v>
+      </c>
+      <c r="C19">
+        <v>1.9</v>
+      </c>
+      <c r="D19">
+        <v>1.9</v>
+      </c>
+      <c r="E19">
+        <v>0.6</v>
+      </c>
+      <c r="F19">
+        <v>0.7</v>
+      </c>
+      <c r="G19">
+        <v>0.65</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D698B0E-BA51-4891-9853-C89C70EC335E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/comfortable_speed.xlsx
+++ b/comfortable_speed.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FuttoAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B8C77C-6BB6-4A17-AC7E-118D09BF8FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713D17B1-0B9F-4CCB-BE2B-23DA2CDE3E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-1300" windowWidth="19420" windowHeight="11500" xr2:uid="{FAD0BBB9-9FA6-49EF-9FBB-58039FCA0FAD}"/>
+    <workbookView xWindow="-19310" yWindow="-1300" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{FAD0BBB9-9FA6-49EF-9FBB-58039FCA0FAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Sakai</t>
     <phoneticPr fontId="1"/>
@@ -71,6 +72,56 @@
   </si>
   <si>
     <t>Hara</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Yanagaawa</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sawada</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sakai</t>
+  </si>
+  <si>
+    <t>Kanai</t>
+  </si>
+  <si>
+    <t>Yorii</t>
+  </si>
+  <si>
+    <t>Okumura</t>
+  </si>
+  <si>
+    <t>Hara</t>
+  </si>
+  <si>
+    <t>Yanagawa</t>
+  </si>
+  <si>
+    <t>Kojima</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Advance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Without</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mean</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fr</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -136,6 +187,2333 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Normal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet2!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Sakai</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Kanai</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Yorii</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Okumura</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hara</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Yanagawa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$G$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.9966666666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94166666666666676</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0383333333333333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2916666666666667</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0033333333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DFAA-44C3-9F42-032BB7F796B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Advance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet2!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Sakai</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Kanai</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Yorii</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Okumura</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hara</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Yanagawa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.0816666666666666</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0333333333333334</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2666666666666668</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1066666666666667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97666666666666668</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DFAA-44C3-9F42-032BB7F796B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Without</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet2!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Sakai</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Kanai</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Yorii</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Okumura</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hara</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Yanagawa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.9816666666666668</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.27</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.83200000000000007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DFAA-44C3-9F42-032BB7F796B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1409284992"/>
+        <c:axId val="1282121552"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1409284992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1282121552"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1282121552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.8"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1409284992"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>Fr</a:t>
+            </a:r>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Normal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet2!$B$6:$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Sakai</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Kanai</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Yorii</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Okumura</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hara</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Yanagawa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$7:$G$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.24123527071274051</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.22924426001282389</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25351533657414582</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31101481750536469</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.27317646823833081</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.24367397699563315</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-708E-43A3-8E72-F97F9EC18F76}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Advance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet2!$B$6:$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Sakai</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Kanai</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Yorii</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Okumura</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hara</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Yanagawa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$8:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.26180884731198756</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25156007293442623</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.27467552518065558</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3049951758762286</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.26753565620981073</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.23719759222498507</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-708E-43A3-8E72-F97F9EC18F76}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Without</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet2!$B$6:$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Sakai</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Kanai</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Yorii</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Okumura</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hara</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Yanagawa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$9:$G$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.23760463954816752</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.23046148617218398</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.27101318484491349</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30579779476011337</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.27196772280364795</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20206320484421939</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-708E-43A3-8E72-F97F9EC18F76}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1492069056"/>
+        <c:axId val="1282160912"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1492069056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1282160912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1282160912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1492069056"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>389251</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>160651</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>207735</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A5F0BB4-53C2-E503-7926-50836449A127}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>425263</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>50986</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>189379</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>167714</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="グラフ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA557E7A-EBE6-2AA5-51AA-F7033AA583F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,18 +2833,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D6EEC-EB3D-4750-8DFA-23F2515A2107}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="8" max="8" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B1">
+        <v>1.74</v>
+      </c>
+      <c r="H1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -492,8 +2879,12 @@
         <f>AVERAGE(B2:G2)</f>
         <v>0.9966666666666667</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I2">
+        <f>H2/SQRT(9.81*$B$1)</f>
+        <v>0.24123527071274051</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -519,8 +2910,12 @@
         <f>AVERAGE(B3:G3)</f>
         <v>1.0816666666666666</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I3">
+        <f>H3/SQRT(9.81*$B$1)</f>
+        <v>0.26180884731198756</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -546,13 +2941,20 @@
         <f>AVERAGE(B4:G4)</f>
         <v>0.9816666666666668</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I4">
+        <f>H4/SQRT(9.81*$B$1)</f>
+        <v>0.23760463954816752</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B6">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -578,8 +2980,12 @@
         <f>AVERAGE(B7:G7)</f>
         <v>0.94166666666666676</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I7">
+        <f>H7/SQRT(9.81*$B$6)</f>
+        <v>0.22924426001282389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -602,11 +3008,15 @@
         <v>0.5</v>
       </c>
       <c r="H8">
-        <f t="shared" ref="H3:H19" si="0">AVERAGE(B8:G8)</f>
+        <f t="shared" ref="H8:H29" si="0">AVERAGE(B8:G8)</f>
         <v>1.0333333333333334</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I8">
+        <f>H8/SQRT(9.81*$B$6)</f>
+        <v>0.25156007293442623</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -632,13 +3042,20 @@
         <f>AVERAGE(B9:G9)</f>
         <v>0.94666666666666666</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I9">
+        <f>H9/SQRT(9.81*$B$6)</f>
+        <v>0.23046148617218398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B11">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -664,8 +3081,12 @@
         <f t="shared" si="0"/>
         <v>1.0383333333333333</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I12">
+        <f>H12/SQRT(9.81*$B$11)</f>
+        <v>0.25351533657414582</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -691,8 +3112,12 @@
         <f t="shared" si="0"/>
         <v>1.125</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I13">
+        <f>H13/SQRT(9.81*$B$11)</f>
+        <v>0.27467552518065558</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -718,13 +3143,20 @@
         <f t="shared" si="0"/>
         <v>1.1100000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I14">
+        <f>H14/SQRT(9.81*$B$11)</f>
+        <v>0.27101318484491349</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B16">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -750,8 +3182,12 @@
         <f t="shared" si="0"/>
         <v>1.2916666666666667</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I17">
+        <f>H17/SQRT(9.8*$B$16)</f>
+        <v>0.31101481750536469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -777,8 +3213,12 @@
         <f t="shared" si="0"/>
         <v>1.2666666666666668</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I18">
+        <f>H18/SQRT(9.8*$B$16)</f>
+        <v>0.3049951758762286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -804,24 +3244,247 @@
         <f t="shared" si="0"/>
         <v>1.27</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I19">
+        <f t="shared" ref="I18:I19" si="1">H19/SQRT(9.8*$B$16)</f>
+        <v>0.30579779476011337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B21">
+        <v>1.746</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B22">
+        <v>1.79</v>
+      </c>
+      <c r="C22">
+        <v>1.8</v>
+      </c>
+      <c r="D22">
+        <v>1.74</v>
+      </c>
+      <c r="E22">
+        <v>0.5</v>
+      </c>
+      <c r="F22">
+        <v>0.47</v>
+      </c>
+      <c r="G22">
+        <v>0.48</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I22">
+        <f>H22/SQRT(9.8*$B$21)</f>
+        <v>0.27317646823833081</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B23">
+        <v>1.75</v>
+      </c>
+      <c r="C23">
+        <v>1.75</v>
+      </c>
+      <c r="D23">
+        <v>1.72</v>
+      </c>
+      <c r="E23">
+        <v>0.5</v>
+      </c>
+      <c r="F23">
+        <v>0.45</v>
+      </c>
+      <c r="G23">
+        <v>0.47</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>1.1066666666666667</v>
+      </c>
+      <c r="I23">
+        <f t="shared" ref="I23:I24" si="2">H23/SQRT(9.8*$B$21)</f>
+        <v>0.26753565620981073</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>1.87</v>
+      </c>
+      <c r="C24">
+        <v>1.8</v>
+      </c>
+      <c r="D24">
+        <v>1.83</v>
+      </c>
+      <c r="E24">
+        <v>0.45</v>
+      </c>
+      <c r="F24">
+        <v>0.35</v>
+      </c>
+      <c r="G24">
+        <v>0.45</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>1.125</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>0.27196772280364795</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <v>1.58</v>
+      </c>
+      <c r="C27">
+        <v>1.6</v>
+      </c>
+      <c r="D27">
+        <v>1.6</v>
+      </c>
+      <c r="E27">
+        <v>0.42</v>
+      </c>
+      <c r="F27">
+        <v>0.45</v>
+      </c>
+      <c r="G27">
+        <v>0.37</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>1.0033333333333334</v>
+      </c>
+      <c r="I27">
+        <f>H27/SQRT(9.8*$B$26)</f>
+        <v>0.24367397699563315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>1.6</v>
+      </c>
+      <c r="C28">
+        <v>1.56</v>
+      </c>
+      <c r="D28">
+        <v>1.61</v>
+      </c>
+      <c r="E28">
+        <v>0.35</v>
+      </c>
+      <c r="F28">
+        <v>0.36</v>
+      </c>
+      <c r="G28">
+        <v>0.38</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>0.97666666666666668</v>
+      </c>
+      <c r="I28">
+        <f>H28/SQRT(9.8*$B$26)</f>
+        <v>0.23719759222498507</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>1.5</v>
+      </c>
+      <c r="C29">
+        <v>1.45</v>
+      </c>
+      <c r="D29">
+        <v>0.4</v>
+      </c>
+      <c r="E29">
+        <v>0.41</v>
+      </c>
+      <c r="F29">
+        <v>0.4</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>0.83200000000000007</v>
+      </c>
+      <c r="I29">
+        <f t="shared" ref="I28:I29" si="3">H29/SQRT(9.8*$B$26)</f>
+        <v>0.20206320484421939</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
         <v>3</v>
       </c>
     </row>
@@ -833,10 +3496,196 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D698B0E-BA51-4891-9853-C89C70EC335E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>0.9966666666666667</v>
+      </c>
+      <c r="C2">
+        <v>0.94166666666666676</v>
+      </c>
+      <c r="D2">
+        <v>1.0383333333333333</v>
+      </c>
+      <c r="E2">
+        <v>1.2916666666666667</v>
+      </c>
+      <c r="F2">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="G2">
+        <v>1.0033333333333334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>1.0816666666666666</v>
+      </c>
+      <c r="C3">
+        <v>1.0333333333333334</v>
+      </c>
+      <c r="D3">
+        <v>1.125</v>
+      </c>
+      <c r="E3">
+        <v>1.2666666666666668</v>
+      </c>
+      <c r="F3">
+        <v>1.1066666666666667</v>
+      </c>
+      <c r="G3">
+        <v>0.97666666666666668</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>0.9816666666666668</v>
+      </c>
+      <c r="C4">
+        <v>0.94666666666666666</v>
+      </c>
+      <c r="D4">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E4">
+        <v>1.27</v>
+      </c>
+      <c r="F4">
+        <v>1.125</v>
+      </c>
+      <c r="G4">
+        <v>0.83200000000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0.24123527071274051</v>
+      </c>
+      <c r="C7">
+        <v>0.22924426001282389</v>
+      </c>
+      <c r="D7">
+        <v>0.25351533657414582</v>
+      </c>
+      <c r="E7">
+        <v>0.31101481750536469</v>
+      </c>
+      <c r="F7">
+        <v>0.27317646823833081</v>
+      </c>
+      <c r="G7">
+        <v>0.24367397699563315</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>0.26180884731198756</v>
+      </c>
+      <c r="C8">
+        <v>0.25156007293442623</v>
+      </c>
+      <c r="D8">
+        <v>0.27467552518065558</v>
+      </c>
+      <c r="E8">
+        <v>0.3049951758762286</v>
+      </c>
+      <c r="F8">
+        <v>0.26753565620981073</v>
+      </c>
+      <c r="G8">
+        <v>0.23719759222498507</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>0.23760463954816752</v>
+      </c>
+      <c r="C9">
+        <v>0.23046148617218398</v>
+      </c>
+      <c r="D9">
+        <v>0.27101318484491349</v>
+      </c>
+      <c r="E9">
+        <v>0.30579779476011337</v>
+      </c>
+      <c r="F9">
+        <v>0.27196772280364795</v>
+      </c>
+      <c r="G9">
+        <v>0.20206320484421939</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>